--- a/JsonConverter/ExcelFiles/DNDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/DNDialogue.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
   <si>
     <t>string[]</t>
   </si>
@@ -64,15 +64,6 @@
   </si>
   <si>
     <t>SelectionDialogueIdList</t>
-  </si>
-  <si>
-    <t>"오, 여행자여! 이곳에 온 걸 환영하네."</t>
-  </si>
-  <si>
-    <t>"조심하게나... 높은 곳에서 떨어지면 꽤 아프다네."</t>
-  </si>
-  <si>
-    <t>"자, 이제 저 꼭대기를 향해 떠나보게!"</t>
   </si>
   <si>
     <t>dialogue_mainstream_1_1_400</t>
@@ -91,19 +82,39 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>"또 왔나 자네.."</t>
+    <t>"오, 여행자여! 마침 잘 와줬네..."</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>"점프는 SPACE키라네"</t>
+    <t>"실은 내가 키우던 고양이 두 마리가 글쎄, 저 위로 올라가더니 사라져버렸지 뭔가."</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>"점프는 SPACE키! 꾹 누를수록 더 높이 날아가지!"</t>
+    <t>"한 놈도 아니고 두 놈씩이나... 대체 위에 뭐가 있길래 그러는지 원."</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>"이동은 AD(← →) 키로 할 수 있다네."</t>
+    <t>"부탁이네. 저 위로 올라가서 우리 고양이 두 마리를 찾아와 주게나."</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">"아직 우리 고양이들 못 찾았나? 저 위에 있을 걸세." </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"조심히 다녀오게. 점프는 SPACE, 꾹 누르면 높이 뛴다네."</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"이동은 AD(← →), 점프는 SPACE! 꾹 누를수록 높이 뛴다네. 자, 부탁하네!"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_mainstream_1_1_600</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"점프는 꾹 누를수록 높이 뛰는데, 몸이 떨리기 시작하면 그게 최대로 충전됐다는 신호일세!"</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -454,7 +465,8 @@
   <cols>
     <col min="1" max="1" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="6" width="77.140625" customWidth="1"/>
+    <col min="3" max="3" width="100.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="77.140625" customWidth="1"/>
     <col min="7" max="8" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -528,7 +540,7 @@
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>12</v>
@@ -552,7 +564,7 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="12" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>11</v>
@@ -578,10 +590,10 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="12" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -600,14 +612,14 @@
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>19</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -626,13 +638,15 @@
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="6"/>
+        <v>25</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
@@ -650,15 +664,13 @@
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>21</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="D9" s="4"/>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
@@ -676,17 +688,19 @@
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
+      <c r="D10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="4"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -699,10 +713,14 @@
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A11" s="7"/>
+      <c r="A11" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
+      <c r="C11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="4"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>

--- a/JsonConverter/ExcelFiles/DNDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/DNDialogue.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
   <si>
     <t>string[]</t>
   </si>
@@ -115,6 +115,44 @@
   </si>
   <si>
     <t>"점프는 꾹 누를수록 높이 뛰는데, 몸이 떨리기 시작하면 그게 최대로 충전됐다는 신호일세!"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_mainstream_1_3_100</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"야아오옹"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"우리가 찾던 고양이다! 추르를 줘볼까?"</t>
+  </si>
+  <si>
+    <t>"고양이가 시무룩하게 쳐다본다..."</t>
+  </si>
+  <si>
+    <t>dialogue_mainstream_1_3_200</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_mainstream_1_3_400</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_mainstream_1_3_300</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"냐옹~ (고양이가 기분 좋게 따라온다)"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>준다, 안준다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_mainstream_1_3_300,dialogue_mainstream_1_3_400</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -466,7 +504,9 @@
     <col min="1" max="1" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" customWidth="1"/>
     <col min="3" max="3" width="100.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="77.140625" customWidth="1"/>
+    <col min="4" max="4" width="77.140625" customWidth="1"/>
+    <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="64" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -737,12 +777,18 @@
       <c r="R11" s="3"/>
     </row>
     <row r="12" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A12" s="6"/>
+      <c r="A12" s="4" t="s">
+        <v>28</v>
+      </c>
       <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
+      <c r="C12" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="3"/>
@@ -757,12 +803,20 @@
       <c r="R12" s="3"/>
     </row>
     <row r="13" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A13" s="4"/>
+      <c r="A13" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
+      <c r="C13" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+      <c r="E13" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>37</v>
+      </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
       <c r="I13" s="3"/>
@@ -777,10 +831,14 @@
       <c r="R13" s="3"/>
     </row>
     <row r="14" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A14" s="7"/>
+      <c r="A14" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
+      <c r="C14" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="4"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
@@ -797,9 +855,13 @@
       <c r="R14" s="3"/>
     </row>
     <row r="15" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A15" s="7"/>
+      <c r="A15" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
+      <c r="C15" s="12" t="s">
+        <v>31</v>
+      </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>

--- a/JsonConverter/ExcelFiles/DNDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/DNDialogue.xlsx
@@ -60,61 +60,93 @@
     <t>dialogue_mainstream_1_1_200</t>
   </si>
   <si>
+    <t>SelectionDialogueIdList</t>
+  </si>
+  <si>
+    <t>dialogue_mainstream_1_1_400</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_mainstream_1_1_500</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_mainstream_1_2_100</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_mainstream_1_2_200</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"오, 여행자여! 마침 잘 와줬네..."</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"실은 내가 키우던 고양이 두 마리가 글쎄, 저 위로 올라가더니 사라져버렸지 뭔가."</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"한 놈도 아니고 두 놈씩이나... 대체 위에 뭐가 있길래 그러는지 원."</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"부탁이네. 저 위로 올라가서 우리 고양이 두 마리를 찾아와 주게나."</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">"아직 우리 고양이들 못 찾았나? 저 위에 있을 걸세." </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"조심히 다녀오게. 점프는 SPACE, 꾹 누르면 높이 뛴다네."</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"이동은 AD(← →), 점프는 SPACE! 꾹 누를수록 높이 뛴다네. 자, 부탁하네!"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_mainstream_1_1_600</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"점프는 꾹 누를수록 높이 뛰는데, 몸이 떨리기 시작하면 그게 최대로 충전됐다는 신호일세!"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"야아오옹"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"고양이가 시무룩하게 쳐다본다..."</t>
+  </si>
+  <si>
+    <t>dialogue_mainstream_1_3_200</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_mainstream_1_3_400</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_mainstream_1_3_300</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"냐옹~ (고양이가 기분 좋게 따라온다)"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>준다, 안준다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_mainstream_1_3_300,dialogue_mainstream_1_3_400</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>dialogue_mainstream_1_1_100</t>
-  </si>
-  <si>
-    <t>SelectionDialogueIdList</t>
-  </si>
-  <si>
-    <t>dialogue_mainstream_1_1_400</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dialogue_mainstream_1_1_500</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dialogue_mainstream_1_2_100</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dialogue_mainstream_1_2_200</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>"오, 여행자여! 마침 잘 와줬네..."</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>"실은 내가 키우던 고양이 두 마리가 글쎄, 저 위로 올라가더니 사라져버렸지 뭔가."</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>"한 놈도 아니고 두 놈씩이나... 대체 위에 뭐가 있길래 그러는지 원."</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>"부탁이네. 저 위로 올라가서 우리 고양이 두 마리를 찾아와 주게나."</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">"아직 우리 고양이들 못 찾았나? 저 위에 있을 걸세." </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>"조심히 다녀오게. 점프는 SPACE, 꾹 누르면 높이 뛴다네."</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>"이동은 AD(← →), 점프는 SPACE! 꾹 누를수록 높이 뛴다네. 자, 부탁하네!"</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dialogue_mainstream_1_1_600</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>"점프는 꾹 누를수록 높이 뛰는데, 몸이 떨리기 시작하면 그게 최대로 충전됐다는 신호일세!"</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -122,37 +154,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>"야아오옹"</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>"우리가 찾던 고양이다! 추르를 줘볼까?"</t>
-  </si>
-  <si>
-    <t>"고양이가 시무룩하게 쳐다본다..."</t>
-  </si>
-  <si>
-    <t>dialogue_mainstream_1_3_200</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dialogue_mainstream_1_3_400</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dialogue_mainstream_1_3_300</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>"냐옹~ (고양이가 기분 좋게 따라온다)"</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>준다, 안준다</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dialogue_mainstream_1_3_300,dialogue_mainstream_1_3_400</t>
+    <t>"우리가 찾던 고양이다! 츄르를 줘볼까?"</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -565,7 +567,7 @@
         <v>4</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>2</v>
@@ -576,11 +578,11 @@
     </row>
     <row r="4" spans="1:18" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>12</v>
@@ -604,7 +606,7 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>11</v>
@@ -630,10 +632,10 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -652,14 +654,14 @@
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -678,14 +680,14 @@
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -704,11 +706,11 @@
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6"/>
@@ -728,14 +730,14 @@
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
@@ -754,11 +756,11 @@
     </row>
     <row r="11" spans="1:18" ht="15.75" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="7"/>
@@ -778,14 +780,14 @@
     </row>
     <row r="12" spans="1:18" ht="15.75" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -804,18 +806,18 @@
     </row>
     <row r="13" spans="1:18" ht="15.75" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="12" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="12" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
@@ -832,11 +834,11 @@
     </row>
     <row r="14" spans="1:18" ht="15.75" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="12" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="7"/>
@@ -856,11 +858,11 @@
     </row>
     <row r="15" spans="1:18" ht="15.75" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>

--- a/JsonConverter/ExcelFiles/DNDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/DNDialogue.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="54">
   <si>
     <t>string[]</t>
   </si>
@@ -155,6 +155,69 @@
   </si>
   <si>
     <t>"우리가 찾던 고양이다! 츄르를 줘볼까?"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>UseItemId</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Churu_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GiveItemId</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Cat_1</t>
+  </si>
+  <si>
+    <t>dialogue_mainstream_1_4_100</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_mainstream_1_4_200</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_mainstream_1_4_300</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_mainstream_1_4_400</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_mainstream_1_4_300,dialogue_mainstream_1_4_400</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Cat_2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_mainstream_1_5_100</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"오, 두 녀석 다 데려왔구나! 정말 고맙네!"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_main_guide_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_cat_white_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_cat_cheese_01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -227,7 +290,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -250,13 +313,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -266,9 +344,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -282,6 +357,13 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -500,7 +582,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:R1000"/>
+  <dimension ref="A1:T1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -509,10 +591,12 @@
     <col min="4" max="4" width="77.140625" customWidth="1"/>
     <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="64" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="50.7109375" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.75" customHeight="1">
+    <row r="1" spans="1:20" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -523,8 +607,10 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-    </row>
-    <row r="2" spans="1:18" ht="15.75" customHeight="1">
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:20" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -544,13 +630,17 @@
         <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="15.75" customHeight="1">
+    <row r="3" spans="1:20" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -570,27 +660,33 @@
         <v>13</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="15.75" customHeight="1">
+    <row r="4" spans="1:20" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="12" t="s">
+      <c r="B4" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>18</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
@@ -599,13 +695,17 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
-    </row>
-    <row r="5" spans="1:18" ht="15.75" customHeight="1">
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+    </row>
+    <row r="5" spans="1:20" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="12" t="s">
+      <c r="B5" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="4" t="s">
@@ -615,8 +715,8 @@
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
@@ -625,13 +725,17 @@
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
-    </row>
-    <row r="6" spans="1:18" ht="15.75" customHeight="1">
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+    </row>
+    <row r="6" spans="1:20" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="12" t="s">
+      <c r="B6" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -641,8 +745,8 @@
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
@@ -651,13 +755,17 @@
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
-    </row>
-    <row r="7" spans="1:18" ht="15.75" customHeight="1">
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+    </row>
+    <row r="7" spans="1:20" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="12" t="s">
+      <c r="B7" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>21</v>
       </c>
       <c r="D7" s="4" t="s">
@@ -667,8 +775,8 @@
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
@@ -677,24 +785,28 @@
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
-    </row>
-    <row r="8" spans="1:18" ht="15.75" customHeight="1">
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+    </row>
+    <row r="8" spans="1:20" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="12" t="s">
+      <c r="B8" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
@@ -703,22 +815,26 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" ht="15.75" customHeight="1">
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+    </row>
+    <row r="9" spans="1:20" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6" t="s">
+      <c r="B9" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D9" s="4"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="4"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
@@ -727,24 +843,28 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" ht="15.75" customHeight="1">
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+    </row>
+    <row r="10" spans="1:20" ht="15.75" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6" t="s">
+      <c r="B10" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="4"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -753,22 +873,26 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" ht="15.75" customHeight="1">
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+    </row>
+    <row r="11" spans="1:20" ht="15.75" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7" t="s">
+      <c r="B11" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D11" s="4"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -777,24 +901,28 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" ht="15.75" customHeight="1">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" ht="15.75" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6" t="s">
+      <c r="B12" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -803,26 +931,30 @@
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" ht="15.75" customHeight="1">
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+    </row>
+    <row r="13" spans="1:20" ht="15.75" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="12" t="s">
+      <c r="B13" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>37</v>
       </c>
       <c r="D13" s="4"/>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -831,22 +963,30 @@
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" ht="15.75" customHeight="1">
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+    </row>
+    <row r="14" spans="1:20" ht="15.75" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="12" t="s">
+      <c r="B14" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>32</v>
       </c>
       <c r="D14" s="4"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -855,22 +995,26 @@
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" ht="15.75" customHeight="1">
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+    </row>
+    <row r="15" spans="1:20" ht="15.75" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="12" t="s">
+      <c r="B15" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
@@ -879,220 +1023,342 @@
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-    </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-    </row>
-    <row r="27" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-    </row>
-    <row r="28" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-    </row>
-    <row r="29" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-    </row>
-    <row r="30" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-    </row>
-    <row r="32" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-    </row>
-    <row r="33" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-    </row>
-    <row r="34" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-    </row>
-    <row r="35" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-    </row>
-    <row r="36" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:8" ht="15.75" customHeight="1"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+    </row>
+    <row r="16" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A16" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+      <c r="S17" s="3"/>
+      <c r="T17" s="3"/>
+    </row>
+    <row r="18" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A18" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+    </row>
+    <row r="19" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A19" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A20" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+    </row>
+    <row r="21" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+    </row>
+    <row r="22" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+    </row>
+    <row r="23" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+    </row>
+    <row r="24" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+    </row>
+    <row r="25" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+    </row>
+    <row r="26" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+    </row>
+    <row r="27" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+    </row>
+    <row r="28" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+    </row>
+    <row r="29" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+    </row>
+    <row r="30" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+    </row>
+    <row r="31" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+    </row>
+    <row r="32" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+    </row>
+    <row r="33" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+    </row>
+    <row r="34" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+    </row>
+    <row r="35" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+    </row>
+    <row r="36" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:10" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
